--- a/reports/acdr2026_staff_deployment/ACDR2026_持参物分担一覧_1009案.xlsx
+++ b/reports/acdr2026_staff_deployment/ACDR2026_持参物分担一覧_1009案.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>ポケトークのQRの卓上カード（当日）、名札差替え、急ぎの印刷</t>
+          <t>名札差替え、急ぎの印刷</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>ポケトークのQRは神戸が共有を開始した時点で発行されるため事前印刷はできない。共有開始直後に神戸から届くQR画像を、このプリンターで卓上カードにして塩見・Mizanが置く（10/9会場準備一覧で田中さんから変更）。共有開始を早める案（28日12:20、29日08:30）は神戸と相談。評価フォームのQRなど日時に依らないものは神戸で印刷して持参。Dorsett・EXPOのビジネスセンター有無はSylviaさんに確認（Hotel Miはなし）</t>
+          <t>評価フォームのQRなど日時に依らないものは神戸で印刷して持参。ポケトークのQRは印刷しない（進行スライドとWhatsAppで共有）。Dorsett・EXPOのビジネスセンター有無はSylviaさんに確認（Hotel Miはなし）</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>ホスト運用は神戸（中村）。現地は藤本（神戸から届くQR画像をPPTに貼る）</t>
+          <t>ホスト運用は神戸（中村）。現地は藤本（神戸から届くQR画像を進行スライドに貼り、参加者のWhatsAppに共有）</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1149,17 +1149,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>【TBC】（ATEM所有者・神戸発の職員）</t>
+          <t>荒木田（私物）</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>【TBC】</t>
+          <t>荒木田 NH843（羽田、26日00:25発）</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>業者の回答次第（10/9 WhatsAppで照会）。業者機材でマイナスワンと映像切替ができるなら不要。ATEMの音声入力は3.5mmのマイク入力なので、ミキサーのライン出力を入れるときは変換と音量に注意</t>
+          <t>荒木田の私物を持参（10/9）。業者機材でマイナスワンと映像切替ができる場合は予備。ATEMの音声入力は3.5mmのマイク入力なので、ミキサーのライン出力を入れるときは変換と音量に注意</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>PCは3台（Zoom接続用、進行スライド用、リソース発表用）。AV卓に3台分の電源と机が要る。発表用PC 2系統は業者のスイッチャーに入れ、切替は業者が行う。Zoomへの映像・音声（マイナスワン）を業者機材で行うかATEM Miniを持ち込むかは業者の回答で決める（10/9照会）。</t>
+          <t>PCは3台（Zoom接続用、進行スライド用、リソース発表用）。AV卓に3台分の電源と机が要る。発表用PC 2系統は業者のスイッチャーに入れ、切替は業者が行う。Zoomへの映像切替とマイナスワン音声は荒木田のATEM Miniで行う予定で、業者側の対応可否を照会中（10/9）。</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>羽田発のため神戸の機材は持てない。羽田の免税店で日本酒3本を購入</t>
+          <t>羽田発のため神戸の機材は持てない。羽田の免税店で日本酒3本を購入。ATEM Mini（私物）</t>
         </is>
       </c>
     </row>

--- a/reports/acdr2026_staff_deployment/ACDR2026_持参物分担一覧_1009案.xlsx
+++ b/reports/acdr2026_staff_deployment/ACDR2026_持参物分担一覧_1009案.xlsx
@@ -704,22 +704,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28〜29日Zoom配信。U字の内側（会場中央）に置き、HDMIでAV卓へ</t>
+          <t>持参しない（10/9）。カメラは会場スクリーン用として業者（ExpoAV）のカメラとカメラオペレーターを使う</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>塩見（カメラ本体・バッテリー・SD）、森川部長（三脚）。操作は荒木田</t>
+          <t>―</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>森川部長・塩見TG623（26日）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>神戸の機材は神戸発の職員が運ぶ（荒木田は羽田発）。カメラ本体は手荷物、三脚は預け入れ。乗継ぎがあるので三脚はケースに入れて名札を付ける。U字内に壁コンセントはなく、電源とHDMIはAV卓（前方右）から床配線（経路約12m、手持ちの10mでは足りない見込み）。業者カメラ＋オペレーターを別見積で依頼中。業者カメラなら配線も業者で、ADRCのカメラは予備。</t>
+          <t>業者カメラの映像はスクリーン用スイッチャーを通り、そのHDMI出力をZoom PCのキャプチャで受ける。予備として持参するかは所内で判断</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>手荷物。Webinarホストは神戸（中村さん）、現地は共同ホスト。音声は会場ミキサーのマイナスワン出力（Zoomの戻りを含めない）を使う（神戸のポケトークはこのZoom音声を使う）。映像はカメラとスイッチャー出力をATEM Mini（No.16）で切り替えてUSB入力する案と、業者機材で行う案を業者に照会中（10/9）。ATEMを使う場合、HDMIキャプチャは予備。</t>
+          <t>手荷物。Webinarホストは神戸（中村さん）、現地は共同ホスト。映像は業者スイッチャーのHDMI出力（スクリーンと同じ）をこのキャプチャで受け、音声は業者ミキサーのマイナスワン出力を使う（神戸のポケトークはこのZoom音声を使う）。有線LANはAV卓。</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>荒木田（私物）</t>
+          <t>持参しない（10/9）</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>荒木田 NH843（羽田、26日00:25発）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>荒木田の私物を持参（10/9）。業者機材でマイナスワンと映像切替ができる場合は予備。ATEMの音声入力は3.5mmのマイク入力なので、ミキサーのライン出力を入れるときは変換と音量に注意</t>
+          <t>業者からHDMI出力とマイナスワンの音声ライン出力をもらうため不要（10/9荒木田）</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>PCは3台（Zoom接続用、進行スライド用、リソース発表用）。AV卓に3台分の電源と机が要る。発表用PC 2系統は業者のスイッチャーに入れ、切替は業者が行う。Zoomへの映像切替とマイナスワン音声は荒木田のATEM Miniで行う予定で、業者側の対応可否を照会中（10/9）。</t>
+          <t>PCは3台（Zoom接続用、進行スライド用、リソース発表用）。AV卓に3台分の電源と机が要る。発表用PC 2系統は業者のスイッチャーに入れ、切替は業者が行う。カメラとスイッチャーは会場スクリーン用に業者が用意し、ADRCはHDMI出力・マイナスワンの音声出力・有線LANを受けてZoomに送る（10/9）。</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>羽田発のため神戸の機材は持てない。羽田の免税店で日本酒3本を購入。ATEM Mini（私物）</t>
+          <t>羽田発のため神戸の機材は持てない。羽田の免税店で日本酒3本を購入</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>カメラ本体・三脚、SC資料30冊（森川部長）。バナーフレームの代替候補。乗継ぎありで預け入れは要注意</t>
+          <t>SC資料30冊（森川部長）。バナーフレームの代替候補。乗継ぎありで預け入れは要注意</t>
         </is>
       </c>
     </row>

--- a/reports/acdr2026_staff_deployment/ACDR2026_持参物分担一覧_1009案.xlsx
+++ b/reports/acdr2026_staff_deployment/ACDR2026_持参物分担一覧_1009案.xlsx
@@ -729,7 +729,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Zoom接続用ノートPC＋HDMIキャプチャ＋電源</t>
+          <t>Zoom接続用ノートPC＋電源</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>手荷物。Webinarホストは神戸（中村さん）、現地は共同ホスト。映像は業者スイッチャーのHDMI出力（スクリーンと同じ）をこのキャプチャで受け、音声は業者ミキサーのマイナスワン出力を使う（神戸のポケトークはこのZoom音声を使う）。有線LANはAV卓。</t>
+          <t>手荷物。Webinarホストは神戸（中村さん）、現地は共同ホスト。映像は業者スイッチャーのHDMI出力（スクリーンと同じ）を業者のキャプチャでUSB入力、音声は業者ミキサーのマイナスワン出力を使う（神戸のポケトークはこのZoom音声を使う）。有線LANはAV卓。ADRCはHDMIキャプチャを持っていない見込み（10/9）。手元にあれば予備として持参</t>
         </is>
       </c>
     </row>
